--- a/resultados/adrianopolis/erros_varredura.xlsx
+++ b/resultados/adrianopolis/erros_varredura.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,23 +456,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://www.adrianopolis.pr.gov.br/pagina/78_Historia.html</t>
+          <t>https://www.adrianopolis.pr.gov.br/noticiasView/72994_PREMIACAO-DO-PROJETO--</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>500</v>
+        <v>404</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-29 10:39:05</t>
+          <t>2026-07-29 11:07:48</t>
         </is>
       </c>
     </row>
@@ -484,23 +484,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://www.adrianopolis.pr.gov.br/pagina/193_Atrativos.html</t>
+          <t>https://www.adrianopolis.pr.gov.br/noticiasView/72993_Regulamento-do-Projeto-de-Natal-</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>500</v>
+        <v>404</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-29 10:39:34</t>
+          <t>2026-07-29 11:07:48</t>
         </is>
       </c>
     </row>
@@ -512,23 +512,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://www.adrianopolis.pr.gov.br/pagina/?idPagina=129</t>
+          <t>https://www.adrianopolis.pr.gov.br/noticiasView/72965_APMI-de-Adrianopolis-e-Prefeitura-Municipal-promovem-</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>500</v>
+        <v>404</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-29 10:43:15</t>
+          <t>2026-07-29 11:08:11</t>
         </is>
       </c>
     </row>
@@ -540,23 +540,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://www.adrianopolis.pr.gov.br/uploads/noticia/</t>
+          <t>http://adrianopolis.pr.gov.br/noticiasView/72994_PREMIACAO-DO-PROJETO--</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>HTTP_403</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-29 10:55:55</t>
+          <t>2026-07-29 12:37:31</t>
         </is>
       </c>
     </row>
@@ -568,23 +568,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>http://adrianopolis.pr.gov.br/pagina/78_Historia.html</t>
+          <t>http://adrianopolis.pr.gov.br/noticiasView/72993_Regulamento-do-Projeto-de-Natal-</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>HTTP_500</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>500</v>
+        <v>404</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-29 11:06:11</t>
+          <t>2026-07-29 12:37:31</t>
         </is>
       </c>
     </row>
@@ -596,7 +596,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://www.adrianopolis.pr.gov.br/noticiasView/72994_PREMIACAO-DO-PROJETO--</t>
+          <t>http://adrianopolis.pr.gov.br/noticiasView/72965_APMI-de-Adrianopolis-e-Prefeitura-Municipal-promovem-</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -608,11 +608,11 @@
         <v>404</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-29 11:07:48</t>
+          <t>2026-07-29 12:37:45</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://www.adrianopolis.pr.gov.br/noticiasView/72993_Regulamento-do-Projeto-de-Natal-</t>
+          <t>http://www.adrianopolis.pr.gov.br/noticiasView/72994_PREMIACAO-DO-PROJETO--</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -636,11 +636,11 @@
         <v>404</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-29 11:07:48</t>
+          <t>2026-07-29 13:52:46</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://www.adrianopolis.pr.gov.br/noticiasView/72965_APMI-de-Adrianopolis-e-Prefeitura-Municipal-promovem-</t>
+          <t>http://www.adrianopolis.pr.gov.br/noticiasView/72993_Regulamento-do-Projeto-de-Natal-</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -664,11 +664,11 @@
         <v>404</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-29 11:08:11</t>
+          <t>2026-07-29 13:52:46</t>
         </is>
       </c>
     </row>
@@ -680,23 +680,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://www.adrianopolis.pr.gov.br/legislacaoView/?id=4506</t>
+          <t>http://www.adrianopolis.pr.gov.br/noticiasView/72965_APMI-de-Adrianopolis-e-Prefeitura-Municipal-promovem-</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>HTTP_403</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-29 11:12:49</t>
+          <t>2026-07-29 13:53:04</t>
         </is>
       </c>
     </row>
@@ -708,23 +708,219 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://www.adrianopolis.pr.gov.br/legislacaoView/?id=3864</t>
+          <t>https://www.adrianopolis.pr.gov.br/pagina/78_Historia.html</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>500</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:15:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>https://www.adrianopolis.pr.gov.br/pagina/193_Atrativos.html</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>500</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:15:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>https://www.adrianopolis.pr.gov.br/pagina/?idPagina=129</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>500</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:15:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>https://www.adrianopolis.pr.gov.br/uploads/noticia/</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>HTTP_403</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D14" t="n">
         <v>403</v>
       </c>
-      <c r="E11" t="n">
-        <v>4</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-07-29 11:14:21</t>
+      <c r="E14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:15:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/pagina/78_Historia.html</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>500</v>
+      </c>
+      <c r="E15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:15:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>http://adrianopolis.pr.gov.br/uploads/noticia/</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>HTTP_403</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>403</v>
+      </c>
+      <c r="E16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:16:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/pagina/78_Historia.html</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>500</v>
+      </c>
+      <c r="E17" t="n">
+        <v>5</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:16:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>adrianopolis</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>http://www.adrianopolis.pr.gov.br/uploads/noticia/</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>HTTP_403</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>403</v>
+      </c>
+      <c r="E18" t="n">
+        <v>7</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:16:09</t>
         </is>
       </c>
     </row>
